--- a/data/img/figuritas/Originales/metricas.xlsx
+++ b/data/img/figuritas/Originales/metricas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/22254ca56b479b7e/Coding/Fulbo/fulbo-posiciones/data/img/figuritas/Originales/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="11_F25DC773A252ABDACC104897891B42CA5ADE58FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39637287-1BAB-4D6A-8BD9-F0FBC7B4B911}"/>
+  <xr:revisionPtr revIDLastSave="148" documentId="11_F25DC773A252ABDACC104897891B42CA5ADE58FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04B54A9E-7305-4791-A6B6-2FD8512C47A8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>Benjamín</t>
   </si>
@@ -132,6 +132,24 @@
   </si>
   <si>
     <t>Ruiz Alonzua</t>
+  </si>
+  <si>
+    <t>Equipo</t>
+  </si>
+  <si>
+    <t>CA RIVER PLATE</t>
+  </si>
+  <si>
+    <t>C ATLETICO TUCUMAN</t>
+  </si>
+  <si>
+    <t>CA VELEZ SARFIELD</t>
+  </si>
+  <si>
+    <t>CA SAN MARTIN DE T</t>
+  </si>
+  <si>
+    <t>CA BOCA JUNIORS</t>
   </si>
 </sst>
 </file>
@@ -139,7 +157,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd\-mm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yy;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -180,9 +198,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,16 +481,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="16.77734375" customWidth="1"/>
     <col min="3" max="8" width="4.77734375" customWidth="1"/>
     <col min="9" max="9" width="32.77734375" customWidth="1"/>
     <col min="10" max="10" width="16.77734375" customWidth="1"/>
+    <col min="13" max="13" width="32.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -506,8 +525,11 @@
       <c r="L1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -545,8 +567,11 @@
         <f>G2</f>
         <v>89</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -584,8 +609,11 @@
         <f t="shared" ref="L3:L11" si="3">G3</f>
         <v>90</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -623,8 +651,11 @@
         <f t="shared" si="3"/>
         <v>91</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -662,8 +693,11 @@
         <f t="shared" si="3"/>
         <v>115</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -701,8 +735,11 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -740,8 +777,11 @@
         <f t="shared" si="3"/>
         <v>78</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -779,8 +819,11 @@
         <f t="shared" si="3"/>
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -818,8 +861,11 @@
         <f t="shared" si="3"/>
         <v>78</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -857,8 +903,11 @@
         <f t="shared" si="3"/>
         <v>64</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -896,8 +945,11 @@
         <f t="shared" si="3"/>
         <v>81</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -934,6 +986,9 @@
       <c r="L12">
         <f t="shared" ref="L12" si="7">G12</f>
         <v>113</v>
+      </c>
+      <c r="M12" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/data/img/figuritas/Originales/metricas.xlsx
+++ b/data/img/figuritas/Originales/metricas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/22254ca56b479b7e/Coding/Fulbo/fulbo-posiciones/data/img/figuritas/Originales/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="11_F25DC773A252ABDACC104897891B42CA5ADE58FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04B54A9E-7305-4791-A6B6-2FD8512C47A8}"/>
+  <xr:revisionPtr revIDLastSave="157" documentId="11_F25DC773A252ABDACC104897891B42CA5ADE58FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE3D36C1-E6DA-4C63-ABA3-5FC9393223CF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -216,6 +216,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -481,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="16.77734375" customWidth="1"/>
@@ -972,24 +976,29 @@
         <v>113</v>
       </c>
       <c r="I12" s="2" t="str">
-        <f t="shared" ref="I12" si="4">_xlfn.CONCAT(A12," ",B12)</f>
+        <f t="shared" ref="I12:I13" si="4">_xlfn.CONCAT(A12," ",B12)</f>
         <v>Juan Pablo Ruiz Alonzua</v>
       </c>
       <c r="J12" s="1">
-        <f t="shared" ref="J12" si="5">(DATE(E12,D12,C12))</f>
+        <f t="shared" ref="J12:J13" si="5">(DATE(E12,D12,C12))</f>
         <v>33435</v>
       </c>
       <c r="K12" s="3">
-        <f t="shared" ref="K12" si="6">(100+F12)/100</f>
+        <f t="shared" ref="K12:K13" si="6">(100+F12)/100</f>
         <v>1.75</v>
       </c>
       <c r="L12">
-        <f t="shared" ref="L12" si="7">G12</f>
+        <f t="shared" ref="L12:L13" si="7">G12</f>
         <v>113</v>
       </c>
       <c r="M12" t="s">
         <v>34</v>
       </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I13" s="2"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
